--- a/beelden/20251103_tabellen.xlsx
+++ b/beelden/20251103_tabellen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dairyconsultnl-my.sharepoint.com/personal/albart_dairyconsult_nl/Documents/bedrijf/Dairyconsult_Albart/representatie/presentaties/beelden/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eigenaar\Documents\quarto_presentaties\beelden\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="192" documentId="8_{1F82ABDD-3D27-494A-9E51-99C6DCBB3560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58859AC3-9B67-4716-85BF-022ED895B895}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34F449C-069B-44A6-B86C-582529F78079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25080" yWindow="345" windowWidth="19440" windowHeight="14880" firstSheet="6" activeTab="6" xr2:uid="{E68ABE83-DD2F-47DB-8F8F-CC529626E7CF}"/>
+    <workbookView xWindow="25080" yWindow="345" windowWidth="19440" windowHeight="14880" firstSheet="11" activeTab="12" xr2:uid="{E68ABE83-DD2F-47DB-8F8F-CC529626E7CF}"/>
   </bookViews>
   <sheets>
     <sheet name="tab12cvb" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,9 @@
     <sheet name="tab2kristensen2010" sheetId="10" r:id="rId10"/>
     <sheet name="table1pieper2009" sheetId="11" r:id="rId11"/>
     <sheet name="tab2li2018" sheetId="12" r:id="rId12"/>
+    <sheet name="tab2bauer2025" sheetId="14" r:id="rId13"/>
+    <sheet name="tab4bauer2025" sheetId="16" r:id="rId14"/>
+    <sheet name="tab5bauer2025" sheetId="15" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="570">
   <si>
     <t xml:space="preserve"> 123a </t>
   </si>
@@ -3133,13 +3136,232 @@
   </si>
   <si>
     <t xml:space="preserve"> Puncture resistance</t>
+  </si>
+  <si>
+    <t>&lt;0.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  NEL (MJ/d)</t>
+  </si>
+  <si>
+    <t>0.69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Ether extract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  NFC</t>
+  </si>
+  <si>
+    <t>0.28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ADL</t>
+  </si>
+  <si>
+    <t>0.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ADFom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  aNDFom</t>
+  </si>
+  <si>
+    <t>0.82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  CP</t>
+  </si>
+  <si>
+    <t>Intake of nutrients (kg/d)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Total</t>
+  </si>
+  <si>
+    <t>0.99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Concentrate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Forage</t>
+  </si>
+  <si>
+    <t>Intake of DM (kg/d)</t>
+  </si>
+  <si>
+    <t>P-value</t>
+  </si>
+  <si>
+    <t>SEM</t>
+  </si>
+  <si>
+    <t>Hay</t>
+  </si>
+  <si>
+    <t>Silage</t>
+  </si>
+  <si>
+    <t>0.48</t>
+  </si>
+  <si>
+    <t>Acetate:propionate ratio</t>
+  </si>
+  <si>
+    <t>Iso-valerate (molar %)</t>
+  </si>
+  <si>
+    <t>0.01</t>
+  </si>
+  <si>
+    <t>Valerate (molar %)</t>
+  </si>
+  <si>
+    <t>Iso-butyrate (molar %)</t>
+  </si>
+  <si>
+    <t>0.84</t>
+  </si>
+  <si>
+    <t>Butyrate (molar %)</t>
+  </si>
+  <si>
+    <t>0.72</t>
+  </si>
+  <si>
+    <t>Propionate (molar %)</t>
+  </si>
+  <si>
+    <t>0.04</t>
+  </si>
+  <si>
+    <t>Acetate (molar %)</t>
+  </si>
+  <si>
+    <t>0.64</t>
+  </si>
+  <si>
+    <t>Total VFA (µmol/g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  N balance (g/d)</t>
+  </si>
+  <si>
+    <t>0.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Energy balance (MJ NEL/d)</t>
+  </si>
+  <si>
+    <t>0.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  N efficiency (milk N in % of N intake)</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Feed conversion efficiency (kg ECM/kg DMI)</t>
+  </si>
+  <si>
+    <t>Efficiency &amp; balances</t>
+  </si>
+  <si>
+    <t>0.46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Change over 35 d</t>
+  </si>
+  <si>
+    <t>0.59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  BCS</t>
+  </si>
+  <si>
+    <t>0.31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Change over 35 d (mm)</t>
+  </si>
+  <si>
+    <t>0.34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  BFT (mm)</t>
+  </si>
+  <si>
+    <t>0.93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Change over 35 d (kg)</t>
+  </si>
+  <si>
+    <t>0.43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  BW (kg)</t>
+  </si>
+  <si>
+    <t>BW &amp; body condition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Fat: protein</t>
+  </si>
+  <si>
+    <t>0.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  SCC (×10^3/mL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Urea (mg/100 mL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Lactose yield (kg/d)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Lactose (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Protein (kg/d)</t>
+  </si>
+  <si>
+    <t>0.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Protein (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Fat (kg/d)</t>
+  </si>
+  <si>
+    <t>0.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Fat (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ECM (kg/d)</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Milk (kg/d)</t>
+  </si>
+  <si>
+    <t>Milk parameters</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3172,6 +3394,11 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -3187,7 +3414,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -3195,11 +3422,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3228,6 +3470,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5450,28 +5695,28 @@
         <v>416</v>
       </c>
       <c r="C3">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="D3">
-        <v>23.5</v>
+        <v>235</v>
       </c>
       <c r="E3">
-        <v>18.399999999999999</v>
+        <v>184</v>
       </c>
       <c r="F3">
-        <v>18.5</v>
+        <v>185</v>
       </c>
       <c r="G3">
-        <v>19.100000000000001</v>
+        <v>191</v>
       </c>
       <c r="H3">
-        <v>16.8</v>
+        <v>168</v>
       </c>
       <c r="I3">
-        <v>15.8</v>
+        <v>158</v>
       </c>
       <c r="J3">
-        <v>16.899999999999999</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -5479,28 +5724,28 @@
         <v>417</v>
       </c>
       <c r="C4">
-        <v>3.4</v>
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>4.3</v>
+        <v>43</v>
       </c>
       <c r="E4">
-        <v>4.3</v>
+        <v>43</v>
       </c>
       <c r="F4">
-        <v>12.6</v>
+        <v>126</v>
       </c>
       <c r="G4">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="H4">
-        <v>5.4</v>
+        <v>54</v>
       </c>
       <c r="I4">
-        <v>11.8</v>
+        <v>118</v>
       </c>
       <c r="J4">
-        <v>10.7</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6008,6 +6253,792 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45501E61-1C0F-4CFC-9844-5B9344356316}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>518</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>517</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>516</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>513</v>
+      </c>
+      <c r="B3">
+        <v>13.9</v>
+      </c>
+      <c r="C3">
+        <v>16.3</v>
+      </c>
+      <c r="D3">
+        <v>0.45</v>
+      </c>
+      <c r="E3" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>512</v>
+      </c>
+      <c r="B4">
+        <v>3.64</v>
+      </c>
+      <c r="C4">
+        <v>3.64</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>510</v>
+      </c>
+      <c r="B5">
+        <v>17.5</v>
+      </c>
+      <c r="C5">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="D5">
+        <v>0.45</v>
+      </c>
+      <c r="E5" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>508</v>
+      </c>
+      <c r="B7">
+        <v>2.97</v>
+      </c>
+      <c r="C7">
+        <v>2.95</v>
+      </c>
+      <c r="D7">
+        <v>0.05</v>
+      </c>
+      <c r="E7" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>506</v>
+      </c>
+      <c r="B8">
+        <v>8.17</v>
+      </c>
+      <c r="C8">
+        <v>9.36</v>
+      </c>
+      <c r="D8">
+        <v>0.23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>505</v>
+      </c>
+      <c r="B9">
+        <v>4.96</v>
+      </c>
+      <c r="C9">
+        <v>5.16</v>
+      </c>
+      <c r="D9">
+        <v>0.13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>503</v>
+      </c>
+      <c r="B10">
+        <v>0.49</v>
+      </c>
+      <c r="C10">
+        <v>0.47</v>
+      </c>
+      <c r="D10">
+        <v>0.01</v>
+      </c>
+      <c r="E10" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>501</v>
+      </c>
+      <c r="B11">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="C11">
+        <v>5.17</v>
+      </c>
+      <c r="D11">
+        <v>0.1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>500</v>
+      </c>
+      <c r="B12">
+        <v>0.77</v>
+      </c>
+      <c r="C12">
+        <v>0.78</v>
+      </c>
+      <c r="D12">
+        <v>0.01</v>
+      </c>
+      <c r="E12" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>498</v>
+      </c>
+      <c r="B13">
+        <v>104</v>
+      </c>
+      <c r="C13">
+        <v>117</v>
+      </c>
+      <c r="D13">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="E13" t="s">
+        <v>497</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C0BD8A8-D52F-43AF-92E6-4201BBEEE9EB}">
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>518</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>517</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>516</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>568</v>
+      </c>
+      <c r="B3">
+        <v>25.9</v>
+      </c>
+      <c r="C3">
+        <v>27.4</v>
+      </c>
+      <c r="D3">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="E3" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>566</v>
+      </c>
+      <c r="B4">
+        <v>25.2</v>
+      </c>
+      <c r="C4">
+        <v>28.1</v>
+      </c>
+      <c r="D4">
+        <v>0.61</v>
+      </c>
+      <c r="E4" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>565</v>
+      </c>
+      <c r="B5">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="C5">
+        <v>4.37</v>
+      </c>
+      <c r="D5">
+        <v>0.08</v>
+      </c>
+      <c r="E5" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>563</v>
+      </c>
+      <c r="B6">
+        <v>1.07</v>
+      </c>
+      <c r="C6">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="D6">
+        <v>0.02</v>
+      </c>
+      <c r="E6" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>562</v>
+      </c>
+      <c r="B7">
+        <v>2.98</v>
+      </c>
+      <c r="C7">
+        <v>3.09</v>
+      </c>
+      <c r="D7">
+        <v>0.05</v>
+      </c>
+      <c r="E7" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>560</v>
+      </c>
+      <c r="B8">
+        <v>0.76</v>
+      </c>
+      <c r="C8">
+        <v>0.84</v>
+      </c>
+      <c r="D8">
+        <v>0.02</v>
+      </c>
+      <c r="E8" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>559</v>
+      </c>
+      <c r="B9">
+        <v>4.79</v>
+      </c>
+      <c r="C9">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D9">
+        <v>0.02</v>
+      </c>
+      <c r="E9" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>558</v>
+      </c>
+      <c r="B10">
+        <v>1.27</v>
+      </c>
+      <c r="C10">
+        <v>1.31</v>
+      </c>
+      <c r="D10">
+        <v>0.03</v>
+      </c>
+      <c r="E10" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>557</v>
+      </c>
+      <c r="B11">
+        <v>22.5</v>
+      </c>
+      <c r="C11">
+        <v>16.2</v>
+      </c>
+      <c r="D11">
+        <v>0.97</v>
+      </c>
+      <c r="E11" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>556</v>
+      </c>
+      <c r="B12">
+        <v>84.5</v>
+      </c>
+      <c r="C12">
+        <v>82.5</v>
+      </c>
+      <c r="D12">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="E12" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>554</v>
+      </c>
+      <c r="B13">
+        <v>1.39</v>
+      </c>
+      <c r="C13">
+        <v>1.35</v>
+      </c>
+      <c r="D13">
+        <v>0.04</v>
+      </c>
+      <c r="E13" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>552</v>
+      </c>
+      <c r="B15">
+        <v>657</v>
+      </c>
+      <c r="C15">
+        <v>653</v>
+      </c>
+      <c r="D15">
+        <v>3.5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>550</v>
+      </c>
+      <c r="B16">
+        <v>8.89</v>
+      </c>
+      <c r="C16">
+        <v>9.7200000000000006</v>
+      </c>
+      <c r="D16">
+        <v>6.29</v>
+      </c>
+      <c r="E16" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>548</v>
+      </c>
+      <c r="B17">
+        <v>6</v>
+      </c>
+      <c r="C17">
+        <v>7</v>
+      </c>
+      <c r="D17">
+        <v>0.9</v>
+      </c>
+      <c r="E17" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>546</v>
+      </c>
+      <c r="B18">
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="C18">
+        <v>-4</v>
+      </c>
+      <c r="D18">
+        <v>0.12</v>
+      </c>
+      <c r="E18" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>544</v>
+      </c>
+      <c r="B19">
+        <v>3.1</v>
+      </c>
+      <c r="C19">
+        <v>3.01</v>
+      </c>
+      <c r="D19">
+        <v>0.11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>542</v>
+      </c>
+      <c r="B20">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="C20">
+        <v>0.03</v>
+      </c>
+      <c r="D20">
+        <v>0.16</v>
+      </c>
+      <c r="E20" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>539</v>
+      </c>
+      <c r="B22">
+        <v>1.44</v>
+      </c>
+      <c r="C22">
+        <v>1.41</v>
+      </c>
+      <c r="D22">
+        <v>0.11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>537</v>
+      </c>
+      <c r="B23">
+        <v>25.8</v>
+      </c>
+      <c r="C23">
+        <v>28.5</v>
+      </c>
+      <c r="D23">
+        <v>0.01</v>
+      </c>
+      <c r="E23" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>535</v>
+      </c>
+      <c r="B24">
+        <v>-13.8</v>
+      </c>
+      <c r="C24">
+        <v>-8.06</v>
+      </c>
+      <c r="D24">
+        <v>3.39</v>
+      </c>
+      <c r="E24" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>533</v>
+      </c>
+      <c r="B25">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="C25">
+        <v>9.9499999999999993</v>
+      </c>
+      <c r="D25">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="E25" t="s">
+        <v>499</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC142D03-2733-45D7-ABCC-B7EA84A75267}">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>518</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>517</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>516</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B2">
+        <v>6.77</v>
+      </c>
+      <c r="C2">
+        <v>6.59</v>
+      </c>
+      <c r="D2">
+        <v>0.33</v>
+      </c>
+      <c r="E2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>532</v>
+      </c>
+      <c r="B3">
+        <v>38.9</v>
+      </c>
+      <c r="C3">
+        <v>41.4</v>
+      </c>
+      <c r="D3">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="E3" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>530</v>
+      </c>
+      <c r="B4">
+        <v>77.599999999999994</v>
+      </c>
+      <c r="C4">
+        <v>78.3</v>
+      </c>
+      <c r="D4">
+        <v>0.21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>528</v>
+      </c>
+      <c r="B5">
+        <v>14.1</v>
+      </c>
+      <c r="C5">
+        <v>14</v>
+      </c>
+      <c r="D5">
+        <v>0.18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>526</v>
+      </c>
+      <c r="B6">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="C6">
+        <v>4.13</v>
+      </c>
+      <c r="D6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>524</v>
+      </c>
+      <c r="B7">
+        <v>1.78</v>
+      </c>
+      <c r="C7">
+        <v>1.51</v>
+      </c>
+      <c r="D7">
+        <v>0.06</v>
+      </c>
+      <c r="E7" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>523</v>
+      </c>
+      <c r="B8">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="C8">
+        <v>1.02</v>
+      </c>
+      <c r="D8">
+        <v>0.02</v>
+      </c>
+      <c r="E8" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>521</v>
+      </c>
+      <c r="B9">
+        <v>1.36</v>
+      </c>
+      <c r="C9">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="D9">
+        <v>0.05</v>
+      </c>
+      <c r="E9" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>520</v>
+      </c>
+      <c r="B10">
+        <v>5.52</v>
+      </c>
+      <c r="C10">
+        <v>5.61</v>
+      </c>
+      <c r="D10">
+        <v>0.09</v>
+      </c>
+      <c r="E10" t="s">
+        <v>519</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 

--- a/beelden/20251103_tabellen.xlsx
+++ b/beelden/20251103_tabellen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eigenaar\Documents\quarto_presentaties\beelden\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34F449C-069B-44A6-B86C-582529F78079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5AE8C36-1474-4BD0-9142-8BA9F9FA507F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25080" yWindow="345" windowWidth="19440" windowHeight="14880" firstSheet="11" activeTab="12" xr2:uid="{E68ABE83-DD2F-47DB-8F8F-CC529626E7CF}"/>
+    <workbookView xWindow="25080" yWindow="345" windowWidth="19440" windowHeight="14880" firstSheet="10" activeTab="15" xr2:uid="{E68ABE83-DD2F-47DB-8F8F-CC529626E7CF}"/>
   </bookViews>
   <sheets>
     <sheet name="tab12cvb" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <sheet name="tab2bauer2025" sheetId="14" r:id="rId13"/>
     <sheet name="tab4bauer2025" sheetId="16" r:id="rId14"/>
     <sheet name="tab5bauer2025" sheetId="15" r:id="rId15"/>
+    <sheet name="tab2spoelstra1990" sheetId="17" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="583">
   <si>
     <t xml:space="preserve"> 123a </t>
   </si>
@@ -3355,6 +3356,45 @@
   </si>
   <si>
     <t>Milk parameters</t>
+  </si>
+  <si>
+    <t>Nitrate (g/kg)</t>
+  </si>
+  <si>
+    <t>Decrease of OM digestibility (%)</t>
+  </si>
+  <si>
+    <t>Fermentation products (g/kg DM)</t>
+  </si>
+  <si>
+    <t>Lactic acid (g/kg DM)</t>
+  </si>
+  <si>
+    <t>Butyric acid (g/kg DM)</t>
+  </si>
+  <si>
+    <t>Clostridial spores (log units/g)</t>
+  </si>
+  <si>
+    <t>NH3-N (g/kg total-N)</t>
+  </si>
+  <si>
+    <t>DM loss (g/kg DM)</t>
+  </si>
+  <si>
+    <t>Ash (g/kg DM)</t>
+  </si>
+  <si>
+    <t>Dry matter (g/kg)</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>nobutyric</t>
+  </si>
+  <si>
+    <t>yesbutyric</t>
   </si>
 </sst>
 </file>
@@ -7042,6 +7082,140 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBB94B80-27DD-442E-A97D-014D18DED90C}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>580</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>579</v>
+      </c>
+      <c r="B2">
+        <v>268</v>
+      </c>
+      <c r="C2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>578</v>
+      </c>
+      <c r="B3">
+        <v>97</v>
+      </c>
+      <c r="C3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>577</v>
+      </c>
+      <c r="B4">
+        <v>42</v>
+      </c>
+      <c r="C4">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>576</v>
+      </c>
+      <c r="B5">
+        <v>132</v>
+      </c>
+      <c r="C5">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>575</v>
+      </c>
+      <c r="B6">
+        <v>2.75</v>
+      </c>
+      <c r="C6">
+        <v>4.8899999999999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>574</v>
+      </c>
+      <c r="B7">
+        <v>1.7</v>
+      </c>
+      <c r="C7">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>573</v>
+      </c>
+      <c r="B8">
+        <v>39.9</v>
+      </c>
+      <c r="C8">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>572</v>
+      </c>
+      <c r="B9">
+        <v>83</v>
+      </c>
+      <c r="C9">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>571</v>
+      </c>
+      <c r="B10">
+        <v>1.6</v>
+      </c>
+      <c r="C10">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>570</v>
+      </c>
+      <c r="B11">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1841F0BA-9EC5-498C-8D6C-DC30F2B7A78A}">
   <dimension ref="A1:H10"/>

--- a/beelden/20251103_tabellen.xlsx
+++ b/beelden/20251103_tabellen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eigenaar\Documents\quarto_presentaties\beelden\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5AE8C36-1474-4BD0-9142-8BA9F9FA507F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{852EF849-3D89-4AA6-A98E-A85C34003203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25080" yWindow="345" windowWidth="19440" windowHeight="14880" firstSheet="10" activeTab="15" xr2:uid="{E68ABE83-DD2F-47DB-8F8F-CC529626E7CF}"/>
+    <workbookView xWindow="25080" yWindow="345" windowWidth="19440" windowHeight="14880" firstSheet="13" activeTab="16" xr2:uid="{E68ABE83-DD2F-47DB-8F8F-CC529626E7CF}"/>
   </bookViews>
   <sheets>
     <sheet name="tab12cvb" sheetId="1" r:id="rId1"/>
@@ -29,6 +29,7 @@
     <sheet name="tab4bauer2025" sheetId="16" r:id="rId14"/>
     <sheet name="tab5bauer2025" sheetId="15" r:id="rId15"/>
     <sheet name="tab2spoelstra1990" sheetId="17" r:id="rId16"/>
+    <sheet name="tab1godden2024" sheetId="18" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="597">
   <si>
     <t xml:space="preserve"> 123a </t>
   </si>
@@ -3395,6 +3396,48 @@
   </si>
   <si>
     <t>yesbutyric</t>
+  </si>
+  <si>
+    <t>AVLS</t>
+  </si>
+  <si>
+    <t>IMI</t>
+  </si>
+  <si>
+    <t>NIMI</t>
+  </si>
+  <si>
+    <t>CRON</t>
+  </si>
+  <si>
+    <t>Intercept</t>
+  </si>
+  <si>
+    <t>Composted</t>
+  </si>
+  <si>
+    <t>Digested</t>
+  </si>
+  <si>
+    <t>Dried</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>Zomer</t>
+  </si>
+  <si>
+    <t>Winter</t>
+  </si>
+  <si>
+    <t>Slechte ventilatie</t>
+  </si>
+  <si>
+    <t>Goede ventilatie</t>
+  </si>
+  <si>
+    <t>Hygiene stal</t>
   </si>
 </sst>
 </file>
@@ -7216,6 +7259,173 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92AFC7B9-6F45-4CF4-9B14-7C6E0FAB1749}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B1" t="s">
+        <v>583</v>
+      </c>
+      <c r="C1" t="s">
+        <v>584</v>
+      </c>
+      <c r="D1" t="s">
+        <v>585</v>
+      </c>
+      <c r="E1" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>587</v>
+      </c>
+      <c r="B2">
+        <v>2.67</v>
+      </c>
+      <c r="C2">
+        <v>29.96</v>
+      </c>
+      <c r="D2">
+        <v>10.65</v>
+      </c>
+      <c r="E2">
+        <v>20.72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>588</v>
+      </c>
+      <c r="B3">
+        <v>-0.74</v>
+      </c>
+      <c r="C3">
+        <v>-11.46</v>
+      </c>
+      <c r="D3">
+        <v>-3.06</v>
+      </c>
+      <c r="E3">
+        <v>-7.51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>589</v>
+      </c>
+      <c r="B4">
+        <v>-0.26</v>
+      </c>
+      <c r="C4">
+        <v>-2.1</v>
+      </c>
+      <c r="D4">
+        <v>0.27</v>
+      </c>
+      <c r="E4">
+        <v>-1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>590</v>
+      </c>
+      <c r="B5">
+        <v>-0.78</v>
+      </c>
+      <c r="C5">
+        <v>-8.61</v>
+      </c>
+      <c r="D5">
+        <v>-3.81</v>
+      </c>
+      <c r="E5">
+        <v>-7.44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>591</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>592</v>
+      </c>
+      <c r="C7">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>594</v>
+      </c>
+      <c r="B9">
+        <v>0.45</v>
+      </c>
+      <c r="C9">
+        <v>6.81</v>
+      </c>
+      <c r="D9">
+        <v>4.38</v>
+      </c>
+      <c r="E9">
+        <v>4.91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>595</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>596</v>
+      </c>
+      <c r="C11">
+        <v>-3.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1841F0BA-9EC5-498C-8D6C-DC30F2B7A78A}">
   <dimension ref="A1:H10"/>

--- a/beelden/20251103_tabellen.xlsx
+++ b/beelden/20251103_tabellen.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eigenaar\Documents\quarto_presentaties\beelden\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dairyconsultnl-my.sharepoint.com/personal/albart_dairyconsult_nl/Documents/Documenten/online_dingen/quarto_presentaties/beelden/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{852EF849-3D89-4AA6-A98E-A85C34003203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="89" documentId="13_ncr:1_{852EF849-3D89-4AA6-A98E-A85C34003203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFB8975A-F050-4931-8DF6-BFA42522FBCE}"/>
   <bookViews>
-    <workbookView xWindow="25080" yWindow="345" windowWidth="19440" windowHeight="14880" firstSheet="13" activeTab="16" xr2:uid="{E68ABE83-DD2F-47DB-8F8F-CC529626E7CF}"/>
+    <workbookView xWindow="25080" yWindow="345" windowWidth="19440" windowHeight="14880" firstSheet="15" activeTab="18" xr2:uid="{E68ABE83-DD2F-47DB-8F8F-CC529626E7CF}"/>
   </bookViews>
   <sheets>
     <sheet name="tab12cvb" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,8 @@
     <sheet name="tab5bauer2025" sheetId="15" r:id="rId15"/>
     <sheet name="tab2spoelstra1990" sheetId="17" r:id="rId16"/>
     <sheet name="tab1godden2024" sheetId="18" r:id="rId17"/>
+    <sheet name="tab3_baumgard_2001" sheetId="19" r:id="rId18"/>
+    <sheet name="tab_3_parales_2025" sheetId="20" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="611">
   <si>
     <t xml:space="preserve"> 123a </t>
   </si>
@@ -3438,6 +3440,48 @@
   </si>
   <si>
     <t>Hygiene stal</t>
+  </si>
+  <si>
+    <t>Opname (kg/dag)</t>
+  </si>
+  <si>
+    <t>Vet (%)</t>
+  </si>
+  <si>
+    <t>Vet (g/dag)</t>
+  </si>
+  <si>
+    <t>Prod (kg/dag)</t>
+  </si>
+  <si>
+    <t>Eiwit (%)</t>
+  </si>
+  <si>
+    <t>Eiwit (g/dag)</t>
+  </si>
+  <si>
+    <t>CON</t>
+  </si>
+  <si>
+    <t>C16:0</t>
+  </si>
+  <si>
+    <t>Chroom</t>
+  </si>
+  <si>
+    <t>C16:0 + Chroom</t>
+  </si>
+  <si>
+    <t>Insulin (muIU)</t>
+  </si>
+  <si>
+    <t>Glucose (mg/dL)</t>
+  </si>
+  <si>
+    <t>NEFA (mmol/L)</t>
+  </si>
+  <si>
+    <t>BHB (mg/dL)</t>
   </si>
 </sst>
 </file>
@@ -7426,6 +7470,230 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9657C23B-AA6B-457C-86AD-A56988455D9A}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1">
+        <v>0</v>
+      </c>
+      <c r="C1">
+        <v>3.5</v>
+      </c>
+      <c r="D1">
+        <v>7</v>
+      </c>
+      <c r="E1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>597</v>
+      </c>
+      <c r="B2">
+        <v>22.7</v>
+      </c>
+      <c r="C2">
+        <v>21.9</v>
+      </c>
+      <c r="D2">
+        <v>19.3</v>
+      </c>
+      <c r="E2">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>600</v>
+      </c>
+      <c r="B3">
+        <v>26.4</v>
+      </c>
+      <c r="C3">
+        <v>26.5</v>
+      </c>
+      <c r="D3">
+        <v>25.8</v>
+      </c>
+      <c r="E3">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>598</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="D4">
+        <v>1.9</v>
+      </c>
+      <c r="E4">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>599</v>
+      </c>
+      <c r="B5">
+        <v>772</v>
+      </c>
+      <c r="C5">
+        <v>579</v>
+      </c>
+      <c r="D5">
+        <v>515</v>
+      </c>
+      <c r="E5">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>601</v>
+      </c>
+      <c r="B6">
+        <v>3.02</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>3.1</v>
+      </c>
+      <c r="E6">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>602</v>
+      </c>
+      <c r="B7">
+        <v>799</v>
+      </c>
+      <c r="C7">
+        <v>801</v>
+      </c>
+      <c r="D7">
+        <v>795</v>
+      </c>
+      <c r="E7">
+        <v>720</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C329BB79-F9CE-4EA0-AF6B-DEC5523D273F}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1" t="s">
+        <v>603</v>
+      </c>
+      <c r="C1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E1" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2">
+        <v>4.7</v>
+      </c>
+      <c r="C2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D2">
+        <v>4.04</v>
+      </c>
+      <c r="E2">
+        <v>5.16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>608</v>
+      </c>
+      <c r="B3">
+        <v>69.400000000000006</v>
+      </c>
+      <c r="C3">
+        <v>70.8</v>
+      </c>
+      <c r="D3">
+        <v>69.7</v>
+      </c>
+      <c r="E3">
+        <v>71.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>609</v>
+      </c>
+      <c r="B4">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="C4">
+        <v>0.66</v>
+      </c>
+      <c r="D4">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E4">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>610</v>
+      </c>
+      <c r="B5">
+        <v>6.13</v>
+      </c>
+      <c r="C5">
+        <v>7.32</v>
+      </c>
+      <c r="D5">
+        <v>5.32</v>
+      </c>
+      <c r="E5">
+        <v>6.12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1841F0BA-9EC5-498C-8D6C-DC30F2B7A78A}">
   <dimension ref="A1:H10"/>
